--- a/songs/PhysicalIntro_v1/quelle/struktur.xlsx
+++ b/songs/PhysicalIntro_v1/quelle/struktur.xlsx
@@ -441,17 +441,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,7 +466,7 @@
           <t>Dua Lipa</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Vorspann (alter Code in src/songs.cpp, Song #1): kein Schluss-Black,</t>
         </is>
@@ -480,7 +481,7 @@
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>am Ende Sprung nach Song #2 Physical, alter Part 40 (Strobo auf den Synth-Auftakt vor chorus 1).</t>
         </is>
@@ -495,7 +496,7 @@
       <c r="C3" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Die Takte sind aus den ms des alten Codes gerechnet (Einspieler, nicht im Taktraster).</t>
         </is>
@@ -534,20 +535,25 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Beschreibung</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -569,16 +575,21 @@
         </is>
       </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Schwarz bleibt; zwei bis vier kurze starke Blinder auf markante Schläge des Einspielers (Takt als Zwischenzeile eintragen), der letzte klingt lang über 2 Takte aus.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Einspieler läuft, alles dunkel</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>progBlack(14860, 1)</t>
         </is>
@@ -600,16 +611,21 @@
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Lauftext "Nerds on Fire" bleibt. Dazu Feuer-Impulse, die zwischen Lampe 1 und Lampe 2 hin und her springen (wie in #80).</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>nur Matrix: Lauftext, alle anderen Geräte schwarz (2 Durchläufe)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>progBlack(23400, 2)   (Matrix: progScrollText("Nerds on Fire", 23400, 90, getRandomColor(), 2))</t>
         </is>
@@ -631,16 +647,21 @@
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>14 Takte Schwarz sind lang: Gitarre und Bass zeigen einen Herzschlag in Rot (progHeartbeat), sehr dunkel; ab der Hälfte (Takt 31) kommen Wasserringe auf der Matrix dazu (blenden ein). Blinder auf die 1 des letzten Takts (Takt 38), klingt über die Part-Grenze aus (carry).</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>alles dunkel</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>progBlack(23000, 3)</t>
         </is>
@@ -662,16 +683,21 @@
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Statt Lauftext: "PHYSICAL" auf der Matrix, pulsiert einmal je Takt und blendet jedes Mal aus (pulse 100), Wasserringe darunter; Herzschlag auf Gitarre und Bass wird heller (fade_in). Auf der letzten Viertel (Takt 47,25) starker Blinder als Absprung in den Song. Der Titel-Lauftext kann wie bei #9 beim Einstieg in den Song laufen (trailer_entry).</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>nur Matrix: Lauftext, alle anderen Geräte schwarz</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>progBlack(14440, 100)   (Matrix: progScrollText("Physical by Dua Lipa", 14440, 90, getRandomColor(), 100))</t>
         </is>
@@ -691,7 +717,7 @@
           <t>0 sek. BLACK</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
